--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>유성우</t>
+          <t>우성유</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>윤찬영</t>
+          <t>윤영찬</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>박정규</t>
+          <t>박규정</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>반윤선</t>
+          <t>반선윤</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>김현수</t>
+          <t>김수현</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>박정원</t>
+          <t>박원정</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1682,6 +1682,100 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>hr_viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EMP007</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>이경주</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SK머티리얼즈</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>기업문화담당</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HR기획팀</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>팀원</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>사무직</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>hr_admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EMP008</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>훈윤</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SK머티리얼즈</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>기업문화담당</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HR기획팀</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>팀원</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>사무직</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>hr_admin</t>
         </is>
       </c>
     </row>

--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -1713,7 +1713,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
